--- a/artfynd/A 16388-2023 artfynd.xlsx
+++ b/artfynd/A 16388-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 16388-2023 artfynd.xlsx
+++ b/artfynd/A 16388-2023 artfynd.xlsx
@@ -2376,7 +2376,7 @@
         <v>109244072</v>
       </c>
       <c r="B17" t="n">
-        <v>80221</v>
+        <v>80222</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 16388-2023 artfynd.xlsx
+++ b/artfynd/A 16388-2023 artfynd.xlsx
@@ -2376,7 +2376,7 @@
         <v>109244072</v>
       </c>
       <c r="B17" t="n">
-        <v>80222</v>
+        <v>80223</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 16388-2023 artfynd.xlsx
+++ b/artfynd/A 16388-2023 artfynd.xlsx
@@ -2376,7 +2376,7 @@
         <v>109244072</v>
       </c>
       <c r="B17" t="n">
-        <v>80223</v>
+        <v>80224</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 16388-2023 artfynd.xlsx
+++ b/artfynd/A 16388-2023 artfynd.xlsx
@@ -2376,7 +2376,7 @@
         <v>109244072</v>
       </c>
       <c r="B17" t="n">
-        <v>80224</v>
+        <v>80226</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 16388-2023 artfynd.xlsx
+++ b/artfynd/A 16388-2023 artfynd.xlsx
@@ -2376,7 +2376,7 @@
         <v>109244072</v>
       </c>
       <c r="B17" t="n">
-        <v>80226</v>
+        <v>80227</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 16388-2023 artfynd.xlsx
+++ b/artfynd/A 16388-2023 artfynd.xlsx
@@ -2376,7 +2376,7 @@
         <v>109244072</v>
       </c>
       <c r="B17" t="n">
-        <v>80227</v>
+        <v>80228</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 16388-2023 artfynd.xlsx
+++ b/artfynd/A 16388-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AY42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4270,6 +4270,894 @@
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>133656925</v>
+      </c>
+      <c r="B34" t="n">
+        <v>89300</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>510</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Åstjärnsberget, Åstjärnsberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>621637</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6898466</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>133656001</v>
+      </c>
+      <c r="B35" t="n">
+        <v>91881</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Åstjärnsberget, Åstjärnsberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>621597</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6898440</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>133655831</v>
+      </c>
+      <c r="B36" t="n">
+        <v>91918</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Åstjärnsberget, Åstjärnsberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>621604</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6898504</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>133656495</v>
+      </c>
+      <c r="B37" t="n">
+        <v>75305</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6428</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Rostfläck</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Arthonia vinosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Åstjärnsberget, Åstjärnsberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>621577</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6898343</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>133656157</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79365</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>185</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Åstjärnsberget, Åstjärnsberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>621616</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6898349</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>133655800</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79365</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>185</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Åstjärnsberget, Åstjärnsberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>621600</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6898492</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>133656099</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57958</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Åstjärnsberget, Åstjärnsberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>621634</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6898405</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>133655856</v>
+      </c>
+      <c r="B41" t="n">
+        <v>75433</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Åstjärnsberget, Åstjärnsberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>621604</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6898505</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>133655952</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57958</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Åstjärnsberget, Åstjärnsberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>621604</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6898505</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 16388-2023 artfynd.xlsx
+++ b/artfynd/A 16388-2023 artfynd.xlsx
@@ -4660,10 +4660,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133656157</v>
+        <v>133656099</v>
       </c>
       <c r="B38" t="n">
-        <v>79365</v>
+        <v>57958</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4671,34 +4671,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Åstjärnsberget, Åstjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>621616</v>
+        <v>621634</v>
       </c>
       <c r="R38" t="n">
-        <v>6898349</v>
+        <v>6898405</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4731,6 +4736,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4854,10 +4864,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133656099</v>
+        <v>133656157</v>
       </c>
       <c r="B40" t="n">
-        <v>57958</v>
+        <v>79365</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4865,39 +4875,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Åstjärnsberget, Åstjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>621634</v>
+        <v>621616</v>
       </c>
       <c r="R40" t="n">
-        <v>6898405</v>
+        <v>6898349</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4930,11 +4935,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 16388-2023 artfynd.xlsx
+++ b/artfynd/A 16388-2023 artfynd.xlsx
@@ -4660,10 +4660,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133656099</v>
+        <v>133656157</v>
       </c>
       <c r="B38" t="n">
-        <v>57958</v>
+        <v>79365</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4671,39 +4671,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Åstjärnsberget, Åstjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>621634</v>
+        <v>621616</v>
       </c>
       <c r="R38" t="n">
-        <v>6898405</v>
+        <v>6898349</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4736,11 +4731,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4767,10 +4757,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133655800</v>
+        <v>133656099</v>
       </c>
       <c r="B39" t="n">
-        <v>79365</v>
+        <v>57958</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4778,34 +4768,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Åstjärnsberget, Åstjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>621600</v>
+        <v>621634</v>
       </c>
       <c r="R39" t="n">
-        <v>6898492</v>
+        <v>6898405</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4838,6 +4833,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4864,7 +4864,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133656157</v>
+        <v>133655800</v>
       </c>
       <c r="B40" t="n">
         <v>79365</v>
@@ -4899,10 +4899,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>621616</v>
+        <v>621600</v>
       </c>
       <c r="R40" t="n">
-        <v>6898349</v>
+        <v>6898492</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>

--- a/artfynd/A 16388-2023 artfynd.xlsx
+++ b/artfynd/A 16388-2023 artfynd.xlsx
@@ -4275,7 +4275,7 @@
         <v>133656925</v>
       </c>
       <c r="B34" t="n">
-        <v>89300</v>
+        <v>89302</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>133656001</v>
       </c>
       <c r="B35" t="n">
-        <v>91881</v>
+        <v>91883</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4469,7 +4469,7 @@
         <v>133655831</v>
       </c>
       <c r="B36" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4660,10 +4660,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133656157</v>
+        <v>133656099</v>
       </c>
       <c r="B38" t="n">
-        <v>79365</v>
+        <v>57958</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4671,34 +4671,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Åstjärnsberget, Åstjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>621616</v>
+        <v>621634</v>
       </c>
       <c r="R38" t="n">
-        <v>6898349</v>
+        <v>6898405</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4731,6 +4736,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4757,10 +4767,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133656099</v>
+        <v>133655800</v>
       </c>
       <c r="B39" t="n">
-        <v>57958</v>
+        <v>79366</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4768,39 +4778,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Åstjärnsberget, Åstjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>621634</v>
+        <v>621600</v>
       </c>
       <c r="R39" t="n">
-        <v>6898405</v>
+        <v>6898492</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4833,11 +4838,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4864,10 +4864,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133655800</v>
+        <v>133656157</v>
       </c>
       <c r="B40" t="n">
-        <v>79365</v>
+        <v>79366</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4899,10 +4899,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>621600</v>
+        <v>621616</v>
       </c>
       <c r="R40" t="n">
-        <v>6898492</v>
+        <v>6898349</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>

--- a/artfynd/A 16388-2023 artfynd.xlsx
+++ b/artfynd/A 16388-2023 artfynd.xlsx
@@ -4275,7 +4275,7 @@
         <v>133656925</v>
       </c>
       <c r="B34" t="n">
-        <v>89302</v>
+        <v>89310</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>133656001</v>
       </c>
       <c r="B35" t="n">
-        <v>91883</v>
+        <v>91891</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4469,7 +4469,7 @@
         <v>133655831</v>
       </c>
       <c r="B36" t="n">
-        <v>91920</v>
+        <v>91928</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 16388-2023 artfynd.xlsx
+++ b/artfynd/A 16388-2023 artfynd.xlsx
@@ -4275,7 +4275,7 @@
         <v>133656925</v>
       </c>
       <c r="B34" t="n">
-        <v>89310</v>
+        <v>89328</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>133656001</v>
       </c>
       <c r="B35" t="n">
-        <v>91891</v>
+        <v>91910</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4469,7 +4469,7 @@
         <v>133655831</v>
       </c>
       <c r="B36" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>133656495</v>
       </c>
       <c r="B37" t="n">
-        <v>75305</v>
+        <v>75316</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4663,7 +4663,7 @@
         <v>133656099</v>
       </c>
       <c r="B38" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
         <v>133655800</v>
       </c>
       <c r="B39" t="n">
-        <v>79366</v>
+        <v>79380</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>133656157</v>
       </c>
       <c r="B40" t="n">
-        <v>79366</v>
+        <v>79380</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4964,7 +4964,7 @@
         <v>133655856</v>
       </c>
       <c r="B41" t="n">
-        <v>75433</v>
+        <v>75444</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
         <v>133655952</v>
       </c>
       <c r="B42" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 16388-2023 artfynd.xlsx
+++ b/artfynd/A 16388-2023 artfynd.xlsx
@@ -4767,7 +4767,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133655800</v>
+        <v>133656157</v>
       </c>
       <c r="B39" t="n">
         <v>79380</v>
@@ -4802,10 +4802,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>621600</v>
+        <v>621616</v>
       </c>
       <c r="R39" t="n">
-        <v>6898492</v>
+        <v>6898349</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4864,7 +4864,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133656157</v>
+        <v>133655800</v>
       </c>
       <c r="B40" t="n">
         <v>79380</v>
@@ -4899,10 +4899,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>621616</v>
+        <v>621600</v>
       </c>
       <c r="R40" t="n">
-        <v>6898349</v>
+        <v>6898492</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>

--- a/artfynd/A 16388-2023 artfynd.xlsx
+++ b/artfynd/A 16388-2023 artfynd.xlsx
@@ -4275,7 +4275,7 @@
         <v>133656925</v>
       </c>
       <c r="B34" t="n">
-        <v>89328</v>
+        <v>89338</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>133656001</v>
       </c>
       <c r="B35" t="n">
-        <v>91910</v>
+        <v>91920</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4469,7 +4469,7 @@
         <v>133655831</v>
       </c>
       <c r="B36" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>133656495</v>
       </c>
       <c r="B37" t="n">
-        <v>75316</v>
+        <v>75326</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4663,7 +4663,7 @@
         <v>133656099</v>
       </c>
       <c r="B38" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4767,10 +4767,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133656157</v>
+        <v>133655800</v>
       </c>
       <c r="B39" t="n">
-        <v>79380</v>
+        <v>79390</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4802,10 +4802,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>621616</v>
+        <v>621600</v>
       </c>
       <c r="R39" t="n">
-        <v>6898349</v>
+        <v>6898492</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4864,10 +4864,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133655800</v>
+        <v>133656157</v>
       </c>
       <c r="B40" t="n">
-        <v>79380</v>
+        <v>79390</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4899,10 +4899,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>621600</v>
+        <v>621616</v>
       </c>
       <c r="R40" t="n">
-        <v>6898492</v>
+        <v>6898349</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4964,7 +4964,7 @@
         <v>133655856</v>
       </c>
       <c r="B41" t="n">
-        <v>75444</v>
+        <v>75454</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
         <v>133655952</v>
       </c>
       <c r="B42" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 16388-2023 artfynd.xlsx
+++ b/artfynd/A 16388-2023 artfynd.xlsx
@@ -4275,7 +4275,7 @@
         <v>133656925</v>
       </c>
       <c r="B34" t="n">
-        <v>89338</v>
+        <v>89339</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>133656001</v>
       </c>
       <c r="B35" t="n">
-        <v>91920</v>
+        <v>91922</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4469,7 +4469,7 @@
         <v>133655831</v>
       </c>
       <c r="B36" t="n">
-        <v>91957</v>
+        <v>91959</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4767,10 +4767,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133655800</v>
+        <v>133656157</v>
       </c>
       <c r="B39" t="n">
-        <v>79390</v>
+        <v>79391</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4802,10 +4802,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>621600</v>
+        <v>621616</v>
       </c>
       <c r="R39" t="n">
-        <v>6898492</v>
+        <v>6898349</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4864,10 +4864,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133656157</v>
+        <v>133655800</v>
       </c>
       <c r="B40" t="n">
-        <v>79390</v>
+        <v>79391</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4899,10 +4899,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>621616</v>
+        <v>621600</v>
       </c>
       <c r="R40" t="n">
-        <v>6898349</v>
+        <v>6898492</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>

--- a/artfynd/A 16388-2023 artfynd.xlsx
+++ b/artfynd/A 16388-2023 artfynd.xlsx
@@ -4767,7 +4767,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133656157</v>
+        <v>133655800</v>
       </c>
       <c r="B39" t="n">
         <v>79391</v>
@@ -4802,10 +4802,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>621616</v>
+        <v>621600</v>
       </c>
       <c r="R39" t="n">
-        <v>6898349</v>
+        <v>6898492</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4864,7 +4864,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133655800</v>
+        <v>133656157</v>
       </c>
       <c r="B40" t="n">
         <v>79391</v>
@@ -4899,10 +4899,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>621600</v>
+        <v>621616</v>
       </c>
       <c r="R40" t="n">
-        <v>6898492</v>
+        <v>6898349</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>

--- a/artfynd/A 16388-2023 artfynd.xlsx
+++ b/artfynd/A 16388-2023 artfynd.xlsx
@@ -4660,10 +4660,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133656099</v>
+        <v>133656157</v>
       </c>
       <c r="B38" t="n">
-        <v>57975</v>
+        <v>79391</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4671,39 +4671,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Åstjärnsberget, Åstjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>621634</v>
+        <v>621616</v>
       </c>
       <c r="R38" t="n">
-        <v>6898405</v>
+        <v>6898349</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4736,11 +4731,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4864,10 +4854,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133656157</v>
+        <v>133656099</v>
       </c>
       <c r="B40" t="n">
-        <v>79391</v>
+        <v>57975</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4875,34 +4865,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Åstjärnsberget, Åstjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>621616</v>
+        <v>621634</v>
       </c>
       <c r="R40" t="n">
-        <v>6898349</v>
+        <v>6898405</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4935,6 +4930,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 16388-2023 artfynd.xlsx
+++ b/artfynd/A 16388-2023 artfynd.xlsx
@@ -4275,7 +4275,7 @@
         <v>133656925</v>
       </c>
       <c r="B34" t="n">
-        <v>89340</v>
+        <v>89347</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>133656001</v>
       </c>
       <c r="B35" t="n">
-        <v>91923</v>
+        <v>91930</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4469,7 +4469,7 @@
         <v>133655831</v>
       </c>
       <c r="B36" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>133656495</v>
       </c>
       <c r="B37" t="n">
-        <v>75326</v>
+        <v>75333</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4660,10 +4660,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133656157</v>
+        <v>133656099</v>
       </c>
       <c r="B38" t="n">
-        <v>79391</v>
+        <v>57975</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4671,34 +4671,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Åstjärnsberget, Åstjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>621616</v>
+        <v>621634</v>
       </c>
       <c r="R38" t="n">
-        <v>6898349</v>
+        <v>6898405</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4731,6 +4736,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4760,7 +4770,7 @@
         <v>133655800</v>
       </c>
       <c r="B39" t="n">
-        <v>79391</v>
+        <v>79398</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4854,10 +4864,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133656099</v>
+        <v>133656157</v>
       </c>
       <c r="B40" t="n">
-        <v>57975</v>
+        <v>79398</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4865,39 +4875,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Åstjärnsberget, Åstjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>621634</v>
+        <v>621616</v>
       </c>
       <c r="R40" t="n">
-        <v>6898405</v>
+        <v>6898349</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4930,11 +4935,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4964,7 +4964,7 @@
         <v>133655856</v>
       </c>
       <c r="B41" t="n">
-        <v>75454</v>
+        <v>75461</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 16388-2023 artfynd.xlsx
+++ b/artfynd/A 16388-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY42"/>
+  <dimension ref="A1:AY43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>109244092</v>
+        <v>133655800</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79405</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Åstjärnsberget, Mpd</t>
+          <t>Åstjärnsberget, Åstjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>621727.1818048353</v>
+        <v>621600</v>
       </c>
       <c r="R2" t="n">
-        <v>6898588.435399239</v>
+        <v>6898492</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,50 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>109244089</v>
+        <v>133656157</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79405</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Åstjärnsberget, Mpd</t>
+          <t>Åstjärnsberget, Åstjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>621647.3782682484</v>
+        <v>621616</v>
       </c>
       <c r="R3" t="n">
-        <v>6898518.283142741</v>
+        <v>6898349</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -857,27 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>100-tal bladrosetter</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,53 +869,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>109244093</v>
+        <v>109244072</v>
       </c>
       <c r="B4" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80305</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4361</v>
+        <v>392</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Åstjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>621744.5063451898</v>
+        <v>621598</v>
       </c>
       <c r="R4" t="n">
-        <v>6898665.671888251</v>
+        <v>6898388</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -980,33 +937,17 @@
           <t>2023-05-10</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-05-10</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Fjolårets fruktkroppar, I halvcirkel, antydan till orange mitt i foten, tunnare fruktkropp än dropptaggsvamp samt saknar dropptaggsvampens vita mycel</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF4" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1025,50 +966,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>109244080</v>
+        <v>133656925</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89354</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>510</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Åstjärnsberget, Mpd</t>
+          <t>Åstjärnsberget, Åstjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>621546.8906221989</v>
+        <v>621637</v>
       </c>
       <c r="R5" t="n">
-        <v>6898308.169009101</v>
+        <v>6898466</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1095,22 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,50 +1063,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>109244059</v>
+        <v>109244063</v>
       </c>
       <c r="B6" t="n">
-        <v>89403</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1205</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hökberget, Mpd</t>
+          <t>Åstjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>621622.5468075093</v>
+        <v>621641</v>
       </c>
       <c r="R6" t="n">
-        <v>6898571.108169767</v>
+        <v>6898555</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1210,19 +1131,9 @@
           <t>2023-05-10</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1249,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>109244087</v>
+        <v>109244062</v>
       </c>
       <c r="B7" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1289,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>621709.2396283295</v>
+        <v>621634</v>
       </c>
       <c r="R7" t="n">
-        <v>6898282.262991496</v>
+        <v>6898558</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1322,19 +1228,9 @@
           <t>2023-05-10</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1364,12 +1260,7 @@
         <v>109244084</v>
       </c>
       <c r="B8" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1401,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>621659.1356878366</v>
+        <v>621659</v>
       </c>
       <c r="R8" t="n">
-        <v>6898205.702895723</v>
+        <v>6898206</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1434,19 +1325,9 @@
           <t>2023-05-10</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1473,50 +1354,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>109244076</v>
+        <v>133655831</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91974</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Åstjärnsberget, Mpd</t>
+          <t>Åstjärnsberget, Åstjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>621613.2522891228</v>
+        <v>621604</v>
       </c>
       <c r="R9" t="n">
-        <v>6898375.034292767</v>
+        <v>6898504</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1543,22 +1419,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,15 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>109244097</v>
+        <v>109244059</v>
       </c>
       <c r="B10" t="n">
-        <v>89403</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1621,14 +1482,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Åstjärnsberget, Mpd</t>
+          <t>Hökberget, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>621661.5740225184</v>
+        <v>621623</v>
       </c>
       <c r="R10" t="n">
-        <v>6898578.590558805</v>
+        <v>6898571</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1658,19 +1519,9 @@
           <t>2023-05-10</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1697,37 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>109244074</v>
+        <v>109244071</v>
       </c>
       <c r="B11" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1737,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>621606.3058010642</v>
+        <v>621598</v>
       </c>
       <c r="R11" t="n">
-        <v>6898437.850745883</v>
+        <v>6898382</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1770,19 +1616,9 @@
           <t>2023-05-10</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1809,37 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>109244079</v>
+        <v>109244097</v>
       </c>
       <c r="B12" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1205</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1849,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>621618.6119133343</v>
+        <v>621661</v>
       </c>
       <c r="R12" t="n">
-        <v>6898317.298325739</v>
+        <v>6898578</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1882,19 +1713,9 @@
           <t>2023-05-10</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1921,50 +1742,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>109244096</v>
+        <v>109244093</v>
       </c>
       <c r="B13" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Åstjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>621685.888761885</v>
+        <v>621744</v>
       </c>
       <c r="R13" t="n">
-        <v>6898617.774379675</v>
+        <v>6898666</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1994,27 +1813,23 @@
           <t>2023-05-10</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-05-10</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Fjolårets fruktkroppar, I halvcirkel, antydan till orange mitt i foten, tunnare fruktkropp än dropptaggsvamp samt saknar dropptaggsvampens vita mycel</t>
         </is>
       </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2033,50 +1848,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>109244073</v>
+        <v>133656001</v>
       </c>
       <c r="B14" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91937</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Åstjärnsberget, Mpd</t>
+          <t>Åstjärnsberget, Åstjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>621600.6279078823</v>
+        <v>621597</v>
       </c>
       <c r="R14" t="n">
-        <v>6898400.739876597</v>
+        <v>6898440</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2103,22 +1913,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2145,15 +1945,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>109244091</v>
+        <v>109244074</v>
       </c>
       <c r="B15" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2161,21 +1956,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2185,10 +1980,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>621663.8857190508</v>
+        <v>621606</v>
       </c>
       <c r="R15" t="n">
-        <v>6898553.448316871</v>
+        <v>6898438</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2218,19 +2013,9 @@
           <t>2023-05-10</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2257,48 +2042,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>109244082</v>
+        <v>109244075</v>
       </c>
       <c r="B16" t="n">
-        <v>89777</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6040186</v>
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Åstjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>621657.1272324376</v>
+        <v>621594</v>
       </c>
       <c r="R16" t="n">
-        <v>6898222.449266274</v>
+        <v>6898463</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2328,33 +2110,17 @@
           <t>2023-05-10</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-05-10</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2373,45 +2139,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>109244072</v>
+        <v>133655856</v>
       </c>
       <c r="B17" t="n">
-        <v>80228</v>
+        <v>75468</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>392</v>
+        <v>6426</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Åstjärnsberget, Mpd</t>
+          <t>Åstjärnsberget, Åstjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>621598</v>
+        <v>621604</v>
       </c>
       <c r="R17" t="n">
-        <v>6898388</v>
+        <v>6898505</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2438,12 +2204,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2470,50 +2236,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>109244061</v>
+        <v>133656495</v>
       </c>
       <c r="B18" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75340</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6428</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Åstjärnsberget, Mpd</t>
+          <t>Åstjärnsberget, Åstjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>621627.7198997563</v>
+        <v>621577</v>
       </c>
       <c r="R18" t="n">
-        <v>6898570.360694868</v>
+        <v>6898343</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2540,22 +2301,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2582,37 +2333,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>109244065</v>
+        <v>109244087</v>
       </c>
       <c r="B19" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2622,10 +2368,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>621647.8700138743</v>
+        <v>621709</v>
       </c>
       <c r="R19" t="n">
-        <v>6898543.526902896</v>
+        <v>6898282</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2655,19 +2401,9 @@
           <t>2023-05-10</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2694,15 +2430,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>109244090</v>
+        <v>109244088</v>
       </c>
       <c r="B20" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2710,21 +2441,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2734,10 +2465,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>621652.7229825039</v>
+        <v>621661</v>
       </c>
       <c r="R20" t="n">
-        <v>6898551.643666961</v>
+        <v>6898376</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2767,19 +2498,14 @@
           <t>2023-05-10</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-05-10</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>på brandstubbe</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2806,37 +2532,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>109244086</v>
+        <v>109244095</v>
       </c>
       <c r="B21" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2846,10 +2567,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>621701.3004772791</v>
+        <v>621731</v>
       </c>
       <c r="R21" t="n">
-        <v>6898178.259910405</v>
+        <v>6898655</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2879,24 +2600,9 @@
           <t>2023-05-10</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>nedan lodytor på bergets södra sida</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2923,15 +2629,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>109244062</v>
+        <v>109244090</v>
       </c>
       <c r="B22" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2939,21 +2640,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2963,10 +2664,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>621633.7645781982</v>
+        <v>621653</v>
       </c>
       <c r="R22" t="n">
-        <v>6898558.433262389</v>
+        <v>6898551</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2996,19 +2697,9 @@
           <t>2023-05-10</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3035,15 +2726,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>109244095</v>
+        <v>133655952</v>
       </c>
       <c r="B23" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57975</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3051,34 +2737,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Åstjärnsberget, Mpd</t>
+          <t>Åstjärnsberget, Åstjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>621730.3770948389</v>
+        <v>621604</v>
       </c>
       <c r="R23" t="n">
-        <v>6898655.351409457</v>
+        <v>6898505</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3105,22 +2796,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3147,50 +2828,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>109244083</v>
+        <v>133656099</v>
       </c>
       <c r="B24" t="n">
-        <v>8367</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57975</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106554</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Åstjärnsberget, Mpd</t>
+          <t>Åstjärnsberget, Åstjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>621659.0682814553</v>
+        <v>621634</v>
       </c>
       <c r="R24" t="n">
-        <v>6898207.56923307</v>
+        <v>6898405</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3217,22 +2898,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3259,15 +2935,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>109244071</v>
+        <v>109244083</v>
       </c>
       <c r="B25" t="n">
-        <v>89403</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8444</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3275,21 +2946,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1205</v>
+        <v>106554</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3299,10 +2970,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>621598.0309512526</v>
+        <v>621659</v>
       </c>
       <c r="R25" t="n">
-        <v>6898381.959449068</v>
+        <v>6898208</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3332,19 +3003,9 @@
           <t>2023-05-10</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3371,15 +3032,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>109244064</v>
+        <v>109244061</v>
       </c>
       <c r="B26" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3411,10 +3067,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>621641.1435635574</v>
+        <v>621628</v>
       </c>
       <c r="R26" t="n">
-        <v>6898548.422568244</v>
+        <v>6898570</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3444,19 +3100,9 @@
           <t>2023-05-10</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3483,15 +3129,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>109244069</v>
+        <v>109244064</v>
       </c>
       <c r="B27" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3523,10 +3164,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>621583.4617417348</v>
+        <v>621641</v>
       </c>
       <c r="R27" t="n">
-        <v>6898435.624570373</v>
+        <v>6898548</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3556,19 +3197,9 @@
           <t>2023-05-10</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3595,15 +3226,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>109244067</v>
+        <v>109244065</v>
       </c>
       <c r="B28" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3635,10 +3261,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>621569.6085025202</v>
+        <v>621648</v>
       </c>
       <c r="R28" t="n">
-        <v>6898495.387692269</v>
+        <v>6898543</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3668,19 +3294,9 @@
           <t>2023-05-10</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3707,37 +3323,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>109244075</v>
+        <v>109244066</v>
       </c>
       <c r="B29" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3747,10 +3358,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>621594.1826055803</v>
+        <v>621589</v>
       </c>
       <c r="R29" t="n">
-        <v>6898462.639635165</v>
+        <v>6898494</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3780,19 +3391,9 @@
           <t>2023-05-10</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3819,15 +3420,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>109244066</v>
+        <v>109244067</v>
       </c>
       <c r="B30" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3859,10 +3455,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>621589.7498461347</v>
+        <v>621570</v>
       </c>
       <c r="R30" t="n">
-        <v>6898494.713283697</v>
+        <v>6898496</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3892,19 +3488,9 @@
           <t>2023-05-10</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3931,37 +3517,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>109244088</v>
+        <v>109244069</v>
       </c>
       <c r="B31" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3971,10 +3552,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>621660.9112788999</v>
+        <v>621583</v>
       </c>
       <c r="R31" t="n">
-        <v>6898376.755388371</v>
+        <v>6898436</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4004,24 +3585,9 @@
           <t>2023-05-10</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>på brandstubbe</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4048,37 +3614,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>109244063</v>
+        <v>109244073</v>
       </c>
       <c r="B32" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4088,10 +3649,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>621641.8252601177</v>
+        <v>621601</v>
       </c>
       <c r="R32" t="n">
-        <v>6898555.454366181</v>
+        <v>6898401</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4121,19 +3682,9 @@
           <t>2023-05-10</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4160,15 +3711,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>109244085</v>
+        <v>109244076</v>
       </c>
       <c r="B33" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4200,10 +3746,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>621716.5855928144</v>
+        <v>621613</v>
       </c>
       <c r="R33" t="n">
-        <v>6898182.549759698</v>
+        <v>6898376</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4233,19 +3779,9 @@
           <t>2023-05-10</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4272,45 +3808,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133656925</v>
+        <v>109244079</v>
       </c>
       <c r="B34" t="n">
-        <v>89347</v>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>510</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Åstjärnsberget, Åstjärnsberget, Mpd</t>
+          <t>Åstjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>621637</v>
+        <v>621619</v>
       </c>
       <c r="R34" t="n">
-        <v>6898466</v>
+        <v>6898317</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4337,12 +3873,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2023-05-10</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2023-05-10</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4369,45 +3905,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133656001</v>
+        <v>109244080</v>
       </c>
       <c r="B35" t="n">
-        <v>91930</v>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Åstjärnsberget, Åstjärnsberget, Mpd</t>
+          <t>Åstjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>621597</v>
+        <v>621547</v>
       </c>
       <c r="R35" t="n">
-        <v>6898440</v>
+        <v>6898309</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4434,12 +3970,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2023-05-10</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2023-05-10</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4466,45 +4002,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133655831</v>
+        <v>109244081</v>
       </c>
       <c r="B36" t="n">
-        <v>91967</v>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Åstjärnsberget, Åstjärnsberget, Mpd</t>
+          <t>Åstjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>621604</v>
+        <v>621659</v>
       </c>
       <c r="R36" t="n">
-        <v>6898504</v>
+        <v>6898247</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4531,12 +4067,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2023-05-10</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2023-05-10</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4563,45 +4099,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133656495</v>
+        <v>109244085</v>
       </c>
       <c r="B37" t="n">
-        <v>75333</v>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6428</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Åstjärnsberget, Åstjärnsberget, Mpd</t>
+          <t>Åstjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>621577</v>
+        <v>621717</v>
       </c>
       <c r="R37" t="n">
-        <v>6898343</v>
+        <v>6898182</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4628,12 +4164,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2023-05-10</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2023-05-10</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4660,50 +4196,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133656099</v>
+        <v>109244086</v>
       </c>
       <c r="B38" t="n">
-        <v>57975</v>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Åstjärnsberget, Åstjärnsberget, Mpd</t>
+          <t>Åstjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>621634</v>
+        <v>621702</v>
       </c>
       <c r="R38" t="n">
-        <v>6898405</v>
+        <v>6898178</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4730,17 +4261,17 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2023-05-10</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2023-05-10</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>nedan lodytor på bergets södra sida</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4767,45 +4298,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133655800</v>
+        <v>109244089</v>
       </c>
       <c r="B39" t="n">
-        <v>79398</v>
+        <v>99118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Åstjärnsberget, Åstjärnsberget, Mpd</t>
+          <t>Åstjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>621600</v>
+        <v>621647</v>
       </c>
       <c r="R39" t="n">
-        <v>6898492</v>
+        <v>6898519</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4832,12 +4363,17 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2023-05-10</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2023-05-10</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>100-tal bladrosetter</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4864,45 +4400,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133656157</v>
+        <v>109244091</v>
       </c>
       <c r="B40" t="n">
-        <v>79398</v>
+        <v>99118</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Åstjärnsberget, Åstjärnsberget, Mpd</t>
+          <t>Åstjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>621616</v>
+        <v>621663</v>
       </c>
       <c r="R40" t="n">
-        <v>6898349</v>
+        <v>6898554</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4929,12 +4465,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2023-05-10</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2023-05-10</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4961,45 +4497,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133655856</v>
+        <v>109244092</v>
       </c>
       <c r="B41" t="n">
-        <v>75461</v>
+        <v>99118</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Åstjärnsberget, Åstjärnsberget, Mpd</t>
+          <t>Åstjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>621604</v>
+        <v>621728</v>
       </c>
       <c r="R41" t="n">
-        <v>6898505</v>
+        <v>6898588</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5026,12 +4562,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2023-05-10</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2023-05-10</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5058,50 +4594,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133655952</v>
+        <v>109244096</v>
       </c>
       <c r="B42" t="n">
-        <v>57975</v>
+        <v>99118</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Åstjärnsberget, Åstjärnsberget, Mpd</t>
+          <t>Åstjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>621604</v>
+        <v>621686</v>
       </c>
       <c r="R42" t="n">
-        <v>6898505</v>
+        <v>6898618</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5128,12 +4659,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2023-05-10</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2023-05-10</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5157,6 +4688,112 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>109244082</v>
+      </c>
+      <c r="B43" t="n">
+        <v>92329</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Åstjärnsberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>621657</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6898222</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2023-05-10</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2023-05-10</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16388-2023 artfynd.xlsx
+++ b/artfynd/A 16388-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY43"/>
+  <dimension ref="A1:AZ43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133656495</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109244066</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109244067</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109244069</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109244080</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133655800</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133656157</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109244072</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133656925</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109244063</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109244062</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109244084</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133655831</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109244059</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109244071</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109244097</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2330,6 +2415,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109244093</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2427,6 +2517,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133656001</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2524,6 +2619,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109244074</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2621,6 +2721,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109244075</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2718,6 +2823,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133655856</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2815,6 +2925,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109244087</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2917,6 +3032,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109244088</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3014,6 +3134,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109244095</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3111,6 +3236,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109244090</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3213,6 +3343,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133655952</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3320,6 +3455,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133656099</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3417,6 +3557,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109244083</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3514,6 +3659,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109244061</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3611,6 +3761,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109244064</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3708,6 +3863,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109244065</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3805,6 +3965,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109244073</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3902,6 +4067,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109244076</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3999,6 +4169,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109244079</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4096,6 +4271,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109244081</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4193,6 +4373,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109244085</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4295,6 +4480,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109244086</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4397,6 +4587,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109244089</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4494,6 +4689,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109244091</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4591,6 +4791,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109244092</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4688,6 +4893,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109244096</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4794,8 +5004,57 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109244082</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 16388-2023 artfynd.xlsx
+++ b/artfynd/A 16388-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ43"/>
+  <dimension ref="A1:AZ44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -782,48 +782,64 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>109244066</v>
+        <v>136339033</v>
       </c>
       <c r="B3" t="n">
-        <v>99118</v>
+        <v>57988</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Åstjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>621589</v>
+        <v>621555</v>
       </c>
       <c r="R3" t="n">
-        <v>6898494</v>
+        <v>6898331</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,12 +863,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -878,13 +894,13 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109244066</t>
+          <t>https://artportalen.se/Sighting/136339033</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>109244067</v>
+        <v>109244066</v>
       </c>
       <c r="B4" t="n">
         <v>99118</v>
@@ -919,10 +935,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>621570</v>
+        <v>621589</v>
       </c>
       <c r="R4" t="n">
-        <v>6898496</v>
+        <v>6898494</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -980,13 +996,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109244067</t>
+          <t>https://artportalen.se/Sighting/109244066</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>109244069</v>
+        <v>109244067</v>
       </c>
       <c r="B5" t="n">
         <v>99118</v>
@@ -1021,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>621583</v>
+        <v>621570</v>
       </c>
       <c r="R5" t="n">
-        <v>6898436</v>
+        <v>6898496</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1082,13 +1098,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109244069</t>
+          <t>https://artportalen.se/Sighting/109244067</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>109244080</v>
+        <v>109244069</v>
       </c>
       <c r="B6" t="n">
         <v>99118</v>
@@ -1123,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>621547</v>
+        <v>621583</v>
       </c>
       <c r="R6" t="n">
-        <v>6898309</v>
+        <v>6898436</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1184,51 +1200,51 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109244080</t>
+          <t>https://artportalen.se/Sighting/109244069</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133655800</v>
+        <v>109244080</v>
       </c>
       <c r="B7" t="n">
-        <v>79405</v>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Åstjärnsberget, Åstjärnsberget, Mpd</t>
+          <t>Åstjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>621600</v>
+        <v>621547</v>
       </c>
       <c r="R7" t="n">
-        <v>6898492</v>
+        <v>6898309</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1255,12 +1271,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2023-05-10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2023-05-10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1286,13 +1302,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133655800</t>
+          <t>https://artportalen.se/Sighting/109244080</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133656157</v>
+        <v>133655800</v>
       </c>
       <c r="B8" t="n">
         <v>79405</v>
@@ -1327,10 +1343,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>621616</v>
+        <v>621600</v>
       </c>
       <c r="R8" t="n">
-        <v>6898349</v>
+        <v>6898492</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1388,51 +1404,51 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133656157</t>
+          <t>https://artportalen.se/Sighting/133655800</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>109244072</v>
+        <v>133656157</v>
       </c>
       <c r="B9" t="n">
-        <v>80305</v>
+        <v>79405</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>392</v>
+        <v>185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Åstjärnsberget, Mpd</t>
+          <t>Åstjärnsberget, Åstjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>621598</v>
+        <v>621616</v>
       </c>
       <c r="R9" t="n">
-        <v>6898388</v>
+        <v>6898349</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1459,12 +1475,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1490,51 +1506,51 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109244072</t>
+          <t>https://artportalen.se/Sighting/133656157</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133656925</v>
+        <v>109244072</v>
       </c>
       <c r="B10" t="n">
-        <v>89354</v>
+        <v>80305</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>510</v>
+        <v>392</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Åstjärnsberget, Åstjärnsberget, Mpd</t>
+          <t>Åstjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>621637</v>
+        <v>621598</v>
       </c>
       <c r="R10" t="n">
-        <v>6898466</v>
+        <v>6898388</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1561,12 +1577,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2023-05-10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2023-05-10</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1592,16 +1608,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133656925</t>
+          <t>https://artportalen.se/Sighting/109244072</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>109244063</v>
+        <v>133656925</v>
       </c>
       <c r="B11" t="n">
-        <v>92208</v>
+        <v>89354</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1609,34 +1625,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>510</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Åstjärnsberget, Mpd</t>
+          <t>Åstjärnsberget, Åstjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>621641</v>
+        <v>621637</v>
       </c>
       <c r="R11" t="n">
-        <v>6898555</v>
+        <v>6898466</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1663,12 +1679,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1694,16 +1710,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109244063</t>
+          <t>https://artportalen.se/Sighting/133656925</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>109244062</v>
+        <v>109244063</v>
       </c>
       <c r="B12" t="n">
-        <v>91909</v>
+        <v>92208</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1711,21 +1727,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1751,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>621634</v>
+        <v>621641</v>
       </c>
       <c r="R12" t="n">
-        <v>6898558</v>
+        <v>6898555</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1796,13 +1812,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109244062</t>
+          <t>https://artportalen.se/Sighting/109244063</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>109244084</v>
+        <v>109244062</v>
       </c>
       <c r="B13" t="n">
         <v>91909</v>
@@ -1837,10 +1853,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>621659</v>
+        <v>621634</v>
       </c>
       <c r="R13" t="n">
-        <v>6898206</v>
+        <v>6898558</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1898,16 +1914,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109244084</t>
+          <t>https://artportalen.se/Sighting/109244062</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133655831</v>
+        <v>109244084</v>
       </c>
       <c r="B14" t="n">
-        <v>91974</v>
+        <v>91909</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1935,14 +1951,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Åstjärnsberget, Åstjärnsberget, Mpd</t>
+          <t>Åstjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>621604</v>
+        <v>621659</v>
       </c>
       <c r="R14" t="n">
-        <v>6898504</v>
+        <v>6898206</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1969,12 +1985,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2023-05-10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2023-05-10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2000,51 +2016,51 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133655831</t>
+          <t>https://artportalen.se/Sighting/109244084</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>109244059</v>
+        <v>133655831</v>
       </c>
       <c r="B15" t="n">
-        <v>91920</v>
+        <v>91974</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hökberget, Mpd</t>
+          <t>Åstjärnsberget, Åstjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>621623</v>
+        <v>621604</v>
       </c>
       <c r="R15" t="n">
-        <v>6898571</v>
+        <v>6898504</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2071,12 +2087,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2102,13 +2118,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109244059</t>
+          <t>https://artportalen.se/Sighting/133655831</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>109244071</v>
+        <v>109244059</v>
       </c>
       <c r="B16" t="n">
         <v>91920</v>
@@ -2139,14 +2155,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Åstjärnsberget, Mpd</t>
+          <t>Hökberget, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>621598</v>
+        <v>621623</v>
       </c>
       <c r="R16" t="n">
-        <v>6898382</v>
+        <v>6898571</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2204,13 +2220,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109244071</t>
+          <t>https://artportalen.se/Sighting/109244059</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>109244097</v>
+        <v>109244071</v>
       </c>
       <c r="B17" t="n">
         <v>91920</v>
@@ -2245,10 +2261,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>621661</v>
+        <v>621598</v>
       </c>
       <c r="R17" t="n">
-        <v>6898578</v>
+        <v>6898382</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2306,54 +2322,51 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109244097</t>
+          <t>https://artportalen.se/Sighting/109244071</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>109244093</v>
+        <v>109244097</v>
       </c>
       <c r="B18" t="n">
-        <v>93189</v>
+        <v>91920</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4361</v>
+        <v>1205</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Åstjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>621744</v>
+        <v>621661</v>
       </c>
       <c r="R18" t="n">
-        <v>6898666</v>
+        <v>6898578</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2388,18 +2401,12 @@
           <t>2023-05-10</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Fjolårets fruktkroppar, I halvcirkel, antydan till orange mitt i foten, tunnare fruktkropp än dropptaggsvamp samt saknar dropptaggsvampens vita mycel</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF18" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2417,51 +2424,54 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109244093</t>
+          <t>https://artportalen.se/Sighting/109244097</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133656001</v>
+        <v>109244093</v>
       </c>
       <c r="B19" t="n">
-        <v>91937</v>
+        <v>93189</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>4361</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Åstjärnsberget, Åstjärnsberget, Mpd</t>
+          <t>Åstjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>621597</v>
+        <v>621744</v>
       </c>
       <c r="R19" t="n">
-        <v>6898440</v>
+        <v>6898666</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2488,20 +2498,26 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2023-05-10</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2023-05-10</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Fjolårets fruktkroppar, I halvcirkel, antydan till orange mitt i foten, tunnare fruktkropp än dropptaggsvamp samt saknar dropptaggsvampens vita mycel</t>
         </is>
       </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2519,51 +2535,51 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133656001</t>
+          <t>https://artportalen.se/Sighting/109244093</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>109244074</v>
+        <v>133656001</v>
       </c>
       <c r="B20" t="n">
-        <v>79327</v>
+        <v>91937</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Åstjärnsberget, Mpd</t>
+          <t>Åstjärnsberget, Åstjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>621606</v>
+        <v>621597</v>
       </c>
       <c r="R20" t="n">
-        <v>6898438</v>
+        <v>6898440</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2590,12 +2606,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2621,13 +2637,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109244074</t>
+          <t>https://artportalen.se/Sighting/133656001</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>109244075</v>
+        <v>109244074</v>
       </c>
       <c r="B21" t="n">
         <v>79327</v>
@@ -2662,10 +2678,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>621594</v>
+        <v>621606</v>
       </c>
       <c r="R21" t="n">
-        <v>6898463</v>
+        <v>6898438</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2723,51 +2739,51 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109244075</t>
+          <t>https://artportalen.se/Sighting/109244074</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133655856</v>
+        <v>109244075</v>
       </c>
       <c r="B22" t="n">
-        <v>75468</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Åstjärnsberget, Åstjärnsberget, Mpd</t>
+          <t>Åstjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>621604</v>
+        <v>621594</v>
       </c>
       <c r="R22" t="n">
-        <v>6898505</v>
+        <v>6898463</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2794,12 +2810,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2023-05-10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2023-05-10</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2825,16 +2841,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133655856</t>
+          <t>https://artportalen.se/Sighting/109244075</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>109244087</v>
+        <v>133655856</v>
       </c>
       <c r="B23" t="n">
-        <v>79946</v>
+        <v>75468</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2842,34 +2858,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>6426</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Åstjärnsberget, Mpd</t>
+          <t>Åstjärnsberget, Åstjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>621709</v>
+        <v>621604</v>
       </c>
       <c r="R23" t="n">
-        <v>6898282</v>
+        <v>6898505</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2896,12 +2912,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2927,13 +2943,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109244087</t>
+          <t>https://artportalen.se/Sighting/133655856</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>109244088</v>
+        <v>109244087</v>
       </c>
       <c r="B24" t="n">
         <v>79946</v>
@@ -2968,10 +2984,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>621661</v>
+        <v>621709</v>
       </c>
       <c r="R24" t="n">
-        <v>6898376</v>
+        <v>6898282</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3006,11 +3022,6 @@
           <t>2023-05-10</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>på brandstubbe</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3034,13 +3045,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109244088</t>
+          <t>https://artportalen.se/Sighting/109244087</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>109244095</v>
+        <v>109244088</v>
       </c>
       <c r="B25" t="n">
         <v>79946</v>
@@ -3075,10 +3086,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>621731</v>
+        <v>621661</v>
       </c>
       <c r="R25" t="n">
-        <v>6898655</v>
+        <v>6898376</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3113,6 +3124,11 @@
           <t>2023-05-10</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>på brandstubbe</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3136,16 +3152,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109244095</t>
+          <t>https://artportalen.se/Sighting/109244088</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>109244090</v>
+        <v>109244095</v>
       </c>
       <c r="B26" t="n">
-        <v>80432</v>
+        <v>79946</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3153,21 +3169,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3177,10 +3193,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>621653</v>
+        <v>621731</v>
       </c>
       <c r="R26" t="n">
-        <v>6898551</v>
+        <v>6898655</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3238,16 +3254,16 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109244090</t>
+          <t>https://artportalen.se/Sighting/109244095</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133655952</v>
+        <v>109244090</v>
       </c>
       <c r="B27" t="n">
-        <v>57975</v>
+        <v>80432</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3255,39 +3271,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Åstjärnsberget, Åstjärnsberget, Mpd</t>
+          <t>Åstjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>621604</v>
+        <v>621653</v>
       </c>
       <c r="R27" t="n">
-        <v>6898505</v>
+        <v>6898551</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3314,12 +3325,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2023-05-10</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2023-05-10</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3345,13 +3356,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133655952</t>
+          <t>https://artportalen.se/Sighting/109244090</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133656099</v>
+        <v>133655952</v>
       </c>
       <c r="B28" t="n">
         <v>57975</v>
@@ -3391,10 +3402,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>621634</v>
+        <v>621604</v>
       </c>
       <c r="R28" t="n">
-        <v>6898405</v>
+        <v>6898505</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3429,11 +3440,6 @@
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3457,51 +3463,56 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133656099</t>
+          <t>https://artportalen.se/Sighting/133655952</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>109244083</v>
+        <v>133656099</v>
       </c>
       <c r="B29" t="n">
-        <v>8444</v>
+        <v>57975</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106554</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Åstjärnsberget, Mpd</t>
+          <t>Åstjärnsberget, Åstjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>621659</v>
+        <v>621634</v>
       </c>
       <c r="R29" t="n">
-        <v>6898208</v>
+        <v>6898405</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3528,12 +3539,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3559,38 +3575,38 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109244083</t>
+          <t>https://artportalen.se/Sighting/133656099</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>109244061</v>
+        <v>109244083</v>
       </c>
       <c r="B30" t="n">
-        <v>99118</v>
+        <v>8444</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3600,10 +3616,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>621628</v>
+        <v>621659</v>
       </c>
       <c r="R30" t="n">
-        <v>6898570</v>
+        <v>6898208</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3661,13 +3677,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109244061</t>
+          <t>https://artportalen.se/Sighting/109244083</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>109244064</v>
+        <v>109244061</v>
       </c>
       <c r="B31" t="n">
         <v>99118</v>
@@ -3702,10 +3718,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>621641</v>
+        <v>621628</v>
       </c>
       <c r="R31" t="n">
-        <v>6898548</v>
+        <v>6898570</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3763,13 +3779,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109244064</t>
+          <t>https://artportalen.se/Sighting/109244061</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>109244065</v>
+        <v>109244064</v>
       </c>
       <c r="B32" t="n">
         <v>99118</v>
@@ -3804,10 +3820,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>621648</v>
+        <v>621641</v>
       </c>
       <c r="R32" t="n">
-        <v>6898543</v>
+        <v>6898548</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3865,13 +3881,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109244065</t>
+          <t>https://artportalen.se/Sighting/109244064</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>109244073</v>
+        <v>109244065</v>
       </c>
       <c r="B33" t="n">
         <v>99118</v>
@@ -3906,10 +3922,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>621601</v>
+        <v>621648</v>
       </c>
       <c r="R33" t="n">
-        <v>6898401</v>
+        <v>6898543</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3967,13 +3983,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109244073</t>
+          <t>https://artportalen.se/Sighting/109244065</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>109244076</v>
+        <v>109244073</v>
       </c>
       <c r="B34" t="n">
         <v>99118</v>
@@ -4008,10 +4024,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>621613</v>
+        <v>621601</v>
       </c>
       <c r="R34" t="n">
-        <v>6898376</v>
+        <v>6898401</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4069,13 +4085,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109244076</t>
+          <t>https://artportalen.se/Sighting/109244073</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>109244079</v>
+        <v>109244076</v>
       </c>
       <c r="B35" t="n">
         <v>99118</v>
@@ -4110,10 +4126,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>621619</v>
+        <v>621613</v>
       </c>
       <c r="R35" t="n">
-        <v>6898317</v>
+        <v>6898376</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4171,13 +4187,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109244079</t>
+          <t>https://artportalen.se/Sighting/109244076</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>109244081</v>
+        <v>109244079</v>
       </c>
       <c r="B36" t="n">
         <v>99118</v>
@@ -4212,10 +4228,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>621659</v>
+        <v>621619</v>
       </c>
       <c r="R36" t="n">
-        <v>6898247</v>
+        <v>6898317</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4273,13 +4289,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109244081</t>
+          <t>https://artportalen.se/Sighting/109244079</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>109244085</v>
+        <v>109244081</v>
       </c>
       <c r="B37" t="n">
         <v>99118</v>
@@ -4314,10 +4330,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>621717</v>
+        <v>621659</v>
       </c>
       <c r="R37" t="n">
-        <v>6898182</v>
+        <v>6898247</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4375,13 +4391,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109244085</t>
+          <t>https://artportalen.se/Sighting/109244081</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>109244086</v>
+        <v>109244085</v>
       </c>
       <c r="B38" t="n">
         <v>99118</v>
@@ -4416,10 +4432,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>621702</v>
+        <v>621717</v>
       </c>
       <c r="R38" t="n">
-        <v>6898178</v>
+        <v>6898182</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4454,11 +4470,6 @@
           <t>2023-05-10</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>nedan lodytor på bergets södra sida</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4482,13 +4493,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109244086</t>
+          <t>https://artportalen.se/Sighting/109244085</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>109244089</v>
+        <v>109244086</v>
       </c>
       <c r="B39" t="n">
         <v>99118</v>
@@ -4523,10 +4534,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>621647</v>
+        <v>621702</v>
       </c>
       <c r="R39" t="n">
-        <v>6898519</v>
+        <v>6898178</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4563,7 +4574,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>100-tal bladrosetter</t>
+          <t>nedan lodytor på bergets södra sida</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4589,13 +4600,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109244089</t>
+          <t>https://artportalen.se/Sighting/109244086</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>109244091</v>
+        <v>109244089</v>
       </c>
       <c r="B40" t="n">
         <v>99118</v>
@@ -4630,10 +4641,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>621663</v>
+        <v>621647</v>
       </c>
       <c r="R40" t="n">
-        <v>6898554</v>
+        <v>6898519</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4668,6 +4679,11 @@
           <t>2023-05-10</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>100-tal bladrosetter</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -4691,13 +4707,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109244091</t>
+          <t>https://artportalen.se/Sighting/109244089</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>109244092</v>
+        <v>109244091</v>
       </c>
       <c r="B41" t="n">
         <v>99118</v>
@@ -4732,10 +4748,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>621728</v>
+        <v>621663</v>
       </c>
       <c r="R41" t="n">
-        <v>6898588</v>
+        <v>6898554</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4793,13 +4809,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109244092</t>
+          <t>https://artportalen.se/Sighting/109244091</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>109244096</v>
+        <v>109244092</v>
       </c>
       <c r="B42" t="n">
         <v>99118</v>
@@ -4834,10 +4850,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>621686</v>
+        <v>621728</v>
       </c>
       <c r="R42" t="n">
-        <v>6898618</v>
+        <v>6898588</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4895,54 +4911,51 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109244096</t>
+          <t>https://artportalen.se/Sighting/109244092</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>109244082</v>
+        <v>109244096</v>
       </c>
       <c r="B43" t="n">
-        <v>92329</v>
+        <v>99118</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6040186</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Åstjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>621657</v>
+        <v>621686</v>
       </c>
       <c r="R43" t="n">
-        <v>6898222</v>
+        <v>6898618</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4977,18 +4990,12 @@
           <t>2023-05-10</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5005,6 +5012,117 @@
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109244096</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>109244082</v>
+      </c>
+      <c r="B44" t="n">
+        <v>92329</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Åstjärnsberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>621657</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6898222</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2023-05-10</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2023-05-10</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/109244082</t>
         </is>
@@ -5054,6 +5172,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 16388-2023 artfynd.xlsx
+++ b/artfynd/A 16388-2023 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136339033</v>
       </c>
       <c r="B3" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 16388-2023 artfynd.xlsx
+++ b/artfynd/A 16388-2023 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136339033</v>
       </c>
       <c r="B3" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
